--- a/downloads/korrigierte_referenz/Sprachkurse_2NF.xlsx
+++ b/downloads/korrigierte_referenz/Sprachkurse_2NF.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PERSON" sheetId="1" r:id="Rbc53b290c1fa476c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SPRACHKENNTNIS" sheetId="2" r:id="Re4e33fcb98b249a7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PERSON" sheetId="1" r:id="R9ff665409bd14383"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SPRACHKENNTNIS" sheetId="2" r:id="Rad79296523444dd4"/>
   </x:sheets>
 </x:workbook>
 </file>
